--- a/labs/lab-05-build-a-recruitment-kpi-dashboard-with-copilot/data/BrightPath_Recruitment_Dashboard_Data.xlsx
+++ b/labs/lab-05-build-a-recruitment-kpi-dashboard-with-copilot/data/BrightPath_Recruitment_Dashboard_Data.xlsx
@@ -70,7 +70,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -79,6 +79,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -808,7 +811,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="L2" s="5" t="n">
         <v>55</v>
       </c>
@@ -852,7 +854,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="L3" s="5" t="n">
         <v>38</v>
       </c>
@@ -896,7 +897,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="L4" s="5" t="n">
         <v>6</v>
       </c>
@@ -940,7 +940,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="L5" s="5" t="n">
         <v>38</v>
       </c>
@@ -984,7 +983,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="L6" s="5" t="n">
         <v>38</v>
       </c>
@@ -1028,7 +1026,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="L7" s="5" t="n">
         <v>12</v>
       </c>
@@ -1072,7 +1069,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="L8" s="5" t="n">
         <v>38</v>
       </c>
@@ -1170,7 +1166,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
       <c r="L10" s="5" t="n">
         <v>38</v>
       </c>
@@ -1214,7 +1209,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="L11" s="5" t="n">
         <v>55</v>
       </c>
@@ -1258,7 +1252,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="L12" s="5" t="n">
         <v>38</v>
       </c>
@@ -1302,7 +1295,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
       <c r="L13" s="5" t="n">
         <v>22</v>
       </c>
@@ -1346,7 +1338,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
       <c r="L14" s="5" t="n">
         <v>22</v>
       </c>
@@ -1390,7 +1381,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
       <c r="L15" s="5" t="n">
         <v>31</v>
       </c>
@@ -1434,7 +1424,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
       <c r="L16" s="5" t="n">
         <v>6</v>
       </c>
@@ -1478,7 +1467,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
       <c r="L17" s="5" t="n">
         <v>12</v>
       </c>
@@ -1522,7 +1510,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
       <c r="L18" s="5" t="n">
         <v>9</v>
       </c>
@@ -1566,7 +1553,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
       <c r="L19" s="5" t="n">
         <v>6</v>
       </c>
@@ -1610,7 +1596,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
       <c r="L20" s="5" t="n">
         <v>38</v>
       </c>
@@ -1702,7 +1687,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
       <c r="L22" s="5" t="n">
         <v>12</v>
       </c>
@@ -1746,7 +1730,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
       <c r="L23" s="5" t="n">
         <v>22</v>
       </c>
@@ -1790,7 +1773,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
       <c r="L24" s="5" t="n">
         <v>22</v>
       </c>
@@ -1834,7 +1816,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
       <c r="L25" s="5" t="n">
         <v>38</v>
       </c>
@@ -1878,7 +1859,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
       <c r="L26" s="5" t="n">
         <v>38</v>
       </c>
@@ -1922,7 +1902,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
       <c r="L27" s="5" t="n">
         <v>6</v>
       </c>
@@ -1966,7 +1945,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
       <c r="L28" s="5" t="n">
         <v>22</v>
       </c>
@@ -2010,7 +1988,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
       <c r="L29" s="5" t="n">
         <v>38</v>
       </c>
@@ -2054,7 +2031,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
       <c r="L30" s="5" t="n">
         <v>12</v>
       </c>
@@ -2098,7 +2074,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
       <c r="L31" s="5" t="n">
         <v>31</v>
       </c>
@@ -2142,7 +2117,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
       <c r="L32" s="5" t="n">
         <v>9</v>
       </c>
@@ -2186,7 +2160,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
       <c r="L33" s="5" t="n">
         <v>38</v>
       </c>
@@ -2230,7 +2203,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
       <c r="L34" s="5" t="n">
         <v>6</v>
       </c>
@@ -2274,7 +2246,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
       <c r="L35" s="5" t="n">
         <v>22</v>
       </c>
@@ -2372,7 +2343,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
       <c r="L37" s="5" t="n">
         <v>6</v>
       </c>
@@ -2470,7 +2440,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
       <c r="L39" s="5" t="n">
         <v>12</v>
       </c>
@@ -2514,7 +2483,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
       <c r="L40" s="5" t="n">
         <v>9</v>
       </c>
@@ -2558,7 +2526,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
       <c r="L41" s="5" t="n">
         <v>9</v>
       </c>
@@ -2656,7 +2623,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
       <c r="L43" s="5" t="n">
         <v>38</v>
       </c>
@@ -2700,7 +2666,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
       <c r="L44" s="5" t="n">
         <v>6</v>
       </c>
@@ -2798,7 +2763,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
       <c r="L46" s="5" t="n">
         <v>55</v>
       </c>
@@ -2842,7 +2806,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
       <c r="L47" s="5" t="n">
         <v>38</v>
       </c>
@@ -2886,7 +2849,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
       <c r="L48" s="5" t="n">
         <v>38</v>
       </c>
@@ -2930,7 +2892,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
       <c r="L49" s="5" t="n">
         <v>31</v>
       </c>
@@ -2974,7 +2935,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
       <c r="L50" s="5" t="n">
         <v>22</v>
       </c>
@@ -3018,7 +2978,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
       <c r="L51" s="5" t="n">
         <v>9</v>
       </c>
@@ -3062,7 +3021,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
       <c r="L52" s="5" t="n">
         <v>6</v>
       </c>
@@ -3160,7 +3118,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
       <c r="L54" s="5" t="n">
         <v>22</v>
       </c>
@@ -3204,7 +3161,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
       <c r="L55" s="5" t="n">
         <v>12</v>
       </c>
@@ -3302,7 +3258,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
       <c r="L57" s="5" t="n">
         <v>9</v>
       </c>
@@ -3346,7 +3301,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
       <c r="L58" s="5" t="n">
         <v>55</v>
       </c>
@@ -3390,7 +3344,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
       <c r="L59" s="5" t="n">
         <v>9</v>
       </c>
@@ -3434,7 +3387,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
       <c r="L60" s="5" t="n">
         <v>55</v>
       </c>
@@ -3478,7 +3430,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
       <c r="L61" s="5" t="n">
         <v>12</v>
       </c>
@@ -3522,7 +3473,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
       <c r="L62" s="5" t="n">
         <v>9</v>
       </c>
@@ -3566,7 +3516,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
       <c r="L63" s="5" t="n">
         <v>22</v>
       </c>
@@ -3610,7 +3559,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
       <c r="L64" s="5" t="n">
         <v>55</v>
       </c>
@@ -3708,7 +3656,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
       <c r="L66" s="5" t="n">
         <v>6</v>
       </c>
@@ -3752,7 +3699,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
       <c r="L67" s="5" t="n">
         <v>6</v>
       </c>
@@ -3796,7 +3742,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
       <c r="L68" s="5" t="n">
         <v>9</v>
       </c>
@@ -3840,7 +3785,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
       <c r="L69" s="5" t="n">
         <v>38</v>
       </c>
@@ -3884,7 +3828,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
       <c r="L70" s="5" t="n">
         <v>38</v>
       </c>
@@ -3928,7 +3871,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
       <c r="L71" s="5" t="n">
         <v>12</v>
       </c>
@@ -3972,7 +3914,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
       <c r="L72" s="5" t="n">
         <v>22</v>
       </c>
@@ -4016,7 +3957,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
       <c r="L73" s="5" t="n">
         <v>6</v>
       </c>
@@ -4060,7 +4000,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
       <c r="L74" s="5" t="n">
         <v>6</v>
       </c>
@@ -4104,7 +4043,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
       <c r="L75" s="5" t="n">
         <v>22</v>
       </c>
@@ -4148,7 +4086,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
       <c r="L76" s="5" t="n">
         <v>22</v>
       </c>
@@ -4192,7 +4129,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
       <c r="L77" s="5" t="n">
         <v>38</v>
       </c>
@@ -4290,7 +4226,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
       <c r="L79" s="5" t="n">
         <v>9</v>
       </c>
@@ -4334,7 +4269,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
       <c r="L80" s="5" t="n">
         <v>38</v>
       </c>
@@ -4378,7 +4312,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
       <c r="L81" s="5" t="n">
         <v>38</v>
       </c>
@@ -4422,7 +4355,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
       <c r="L82" s="5" t="n">
         <v>38</v>
       </c>
@@ -4466,7 +4398,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
       <c r="L83" s="5" t="n">
         <v>38</v>
       </c>
@@ -4510,7 +4441,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr"/>
       <c r="L84" s="5" t="n">
         <v>6</v>
       </c>
@@ -4554,7 +4484,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
       <c r="L85" s="5" t="n">
         <v>31</v>
       </c>
@@ -4598,7 +4527,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr"/>
       <c r="L86" s="5" t="n">
         <v>22</v>
       </c>
@@ -4642,7 +4570,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr"/>
       <c r="L87" s="5" t="n">
         <v>38</v>
       </c>
@@ -4686,7 +4613,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
       <c r="L88" s="5" t="n">
         <v>22</v>
       </c>
@@ -4730,7 +4656,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
       <c r="L89" s="5" t="n">
         <v>55</v>
       </c>
@@ -4774,7 +4699,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
       <c r="L90" s="5" t="n">
         <v>38</v>
       </c>
@@ -4818,7 +4742,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
       <c r="L91" s="5" t="n">
         <v>31</v>
       </c>
@@ -4862,7 +4785,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
       <c r="L92" s="5" t="n">
         <v>6</v>
       </c>
@@ -4906,7 +4828,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
       <c r="L93" s="5" t="n">
         <v>6</v>
       </c>
@@ -4950,7 +4871,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
       <c r="L94" s="5" t="n">
         <v>38</v>
       </c>
@@ -4994,7 +4914,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
       <c r="L95" s="5" t="n">
         <v>6</v>
       </c>
@@ -5038,7 +4957,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
       <c r="L96" s="5" t="n">
         <v>22</v>
       </c>
@@ -5082,7 +5000,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr"/>
       <c r="L97" s="5" t="n">
         <v>31</v>
       </c>
@@ -5174,7 +5091,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
       <c r="L99" s="5" t="n">
         <v>22</v>
       </c>
@@ -5272,7 +5188,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr"/>
       <c r="L101" s="5" t="n">
         <v>22</v>
       </c>
@@ -5316,7 +5231,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr"/>
       <c r="L102" s="5" t="n">
         <v>38</v>
       </c>
@@ -5360,7 +5274,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr"/>
       <c r="L103" s="5" t="n">
         <v>38</v>
       </c>
@@ -5404,7 +5317,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr"/>
       <c r="L104" s="5" t="n">
         <v>38</v>
       </c>
@@ -5448,7 +5360,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr"/>
       <c r="L105" s="5" t="n">
         <v>55</v>
       </c>
@@ -5492,7 +5403,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr"/>
       <c r="L106" s="5" t="n">
         <v>12</v>
       </c>
@@ -5536,7 +5446,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr"/>
       <c r="L107" s="5" t="n">
         <v>22</v>
       </c>
@@ -5580,7 +5489,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr"/>
       <c r="L108" s="5" t="n">
         <v>9</v>
       </c>
@@ -5678,7 +5586,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr"/>
       <c r="L110" s="5" t="n">
         <v>22</v>
       </c>
@@ -5722,7 +5629,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr"/>
       <c r="L111" s="5" t="n">
         <v>9</v>
       </c>
@@ -5766,7 +5672,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr"/>
       <c r="L112" s="5" t="n">
         <v>38</v>
       </c>
@@ -5810,7 +5715,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr"/>
       <c r="L113" s="5" t="n">
         <v>55</v>
       </c>
@@ -5854,7 +5758,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr"/>
       <c r="L114" s="5" t="n">
         <v>55</v>
       </c>
@@ -5898,7 +5801,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr"/>
       <c r="L115" s="5" t="n">
         <v>38</v>
       </c>
@@ -5996,7 +5898,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr"/>
       <c r="L117" s="5" t="n">
         <v>12</v>
       </c>
@@ -6040,7 +5941,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr"/>
       <c r="L118" s="5" t="n">
         <v>12</v>
       </c>
@@ -6084,7 +5984,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr"/>
       <c r="L119" s="5" t="n">
         <v>55</v>
       </c>
@@ -6128,7 +6027,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr"/>
       <c r="L120" s="5" t="n">
         <v>38</v>
       </c>
@@ -6172,7 +6070,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr"/>
       <c r="L121" s="5" t="n">
         <v>12</v>
       </c>
@@ -6216,7 +6113,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr"/>
       <c r="L122" s="5" t="n">
         <v>55</v>
       </c>
@@ -6260,7 +6156,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr"/>
       <c r="L123" s="5" t="n">
         <v>6</v>
       </c>
@@ -6304,7 +6199,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr"/>
       <c r="L124" s="5" t="n">
         <v>22</v>
       </c>
@@ -6348,7 +6242,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr"/>
       <c r="L125" s="5" t="n">
         <v>12</v>
       </c>
@@ -6392,7 +6285,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr"/>
       <c r="L126" s="5" t="n">
         <v>38</v>
       </c>
@@ -6436,7 +6328,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr"/>
       <c r="L127" s="5" t="n">
         <v>6</v>
       </c>
@@ -6480,7 +6371,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr"/>
       <c r="L128" s="5" t="n">
         <v>6</v>
       </c>
@@ -6524,7 +6414,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr"/>
       <c r="L129" s="5" t="n">
         <v>22</v>
       </c>
@@ -6568,7 +6457,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr"/>
       <c r="L130" s="5" t="n">
         <v>22</v>
       </c>
@@ -6612,7 +6500,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr"/>
       <c r="L131" s="5" t="n">
         <v>9</v>
       </c>
@@ -6656,7 +6543,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr"/>
       <c r="L132" s="5" t="n">
         <v>9</v>
       </c>
@@ -6700,7 +6586,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr"/>
       <c r="L133" s="5" t="n">
         <v>6</v>
       </c>
@@ -6744,7 +6629,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr"/>
       <c r="L134" s="5" t="n">
         <v>12</v>
       </c>
@@ -6788,7 +6672,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr"/>
       <c r="L135" s="5" t="n">
         <v>12</v>
       </c>
@@ -6832,7 +6715,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr"/>
       <c r="L136" s="5" t="n">
         <v>38</v>
       </c>
@@ -6876,7 +6758,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr"/>
       <c r="L137" s="5" t="n">
         <v>12</v>
       </c>
@@ -6920,7 +6801,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr"/>
       <c r="L138" s="5" t="n">
         <v>9</v>
       </c>
@@ -6964,7 +6844,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr"/>
       <c r="L139" s="5" t="n">
         <v>6</v>
       </c>
@@ -7008,7 +6887,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr"/>
       <c r="L140" s="5" t="n">
         <v>6</v>
       </c>
@@ -7052,7 +6930,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr"/>
       <c r="L141" s="5" t="n">
         <v>22</v>
       </c>
@@ -7096,7 +6973,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr"/>
       <c r="L142" s="5" t="n">
         <v>6</v>
       </c>
@@ -7140,7 +7016,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr"/>
       <c r="L143" s="5" t="n">
         <v>38</v>
       </c>
@@ -7184,7 +7059,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr"/>
       <c r="L144" s="5" t="n">
         <v>12</v>
       </c>
@@ -7276,7 +7150,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr"/>
       <c r="L146" s="5" t="n">
         <v>22</v>
       </c>
@@ -7320,7 +7193,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr"/>
       <c r="L147" s="5" t="n">
         <v>9</v>
       </c>
@@ -7364,7 +7236,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr"/>
       <c r="L148" s="5" t="n">
         <v>22</v>
       </c>
@@ -7408,7 +7279,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr"/>
       <c r="L149" s="5" t="n">
         <v>38</v>
       </c>
@@ -7452,7 +7322,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr"/>
       <c r="L150" s="5" t="n">
         <v>12</v>
       </c>
@@ -7496,7 +7365,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I151" t="inlineStr"/>
       <c r="L151" s="5" t="n">
         <v>55</v>
       </c>
@@ -7540,7 +7408,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I152" t="inlineStr"/>
       <c r="L152" s="5" t="n">
         <v>55</v>
       </c>
@@ -7638,7 +7505,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr"/>
       <c r="L154" s="5" t="n">
         <v>9</v>
       </c>
@@ -7682,7 +7548,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr"/>
       <c r="L155" s="5" t="n">
         <v>22</v>
       </c>
@@ -7726,7 +7591,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr"/>
       <c r="L156" s="5" t="n">
         <v>31</v>
       </c>
@@ -7770,7 +7634,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr"/>
       <c r="L157" s="5" t="n">
         <v>55</v>
       </c>
@@ -7868,7 +7731,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr"/>
       <c r="L159" s="5" t="n">
         <v>38</v>
       </c>
@@ -7912,7 +7774,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr"/>
       <c r="L160" s="5" t="n">
         <v>12</v>
       </c>
@@ -7956,7 +7817,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr"/>
       <c r="L161" s="5" t="n">
         <v>38</v>
       </c>
@@ -8000,7 +7860,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr"/>
       <c r="L162" s="5" t="n">
         <v>38</v>
       </c>
@@ -8044,7 +7903,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr"/>
       <c r="L163" s="5" t="n">
         <v>12</v>
       </c>
@@ -8088,7 +7946,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr"/>
       <c r="L164" s="5" t="n">
         <v>22</v>
       </c>
@@ -8132,7 +7989,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr"/>
       <c r="L165" s="5" t="n">
         <v>22</v>
       </c>
@@ -8176,7 +8032,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr"/>
       <c r="L166" s="5" t="n">
         <v>22</v>
       </c>
@@ -8220,7 +8075,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I167" t="inlineStr"/>
       <c r="L167" s="5" t="n">
         <v>12</v>
       </c>
@@ -8264,7 +8118,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I168" t="inlineStr"/>
       <c r="L168" s="5" t="n">
         <v>38</v>
       </c>
@@ -8308,7 +8161,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I169" t="inlineStr"/>
       <c r="L169" s="5" t="n">
         <v>12</v>
       </c>
@@ -8352,7 +8204,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I170" t="inlineStr"/>
       <c r="L170" s="5" t="n">
         <v>22</v>
       </c>
@@ -8396,7 +8247,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I171" t="inlineStr"/>
       <c r="L171" s="5" t="n">
         <v>22</v>
       </c>
@@ -8440,7 +8290,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I172" t="inlineStr"/>
       <c r="L172" s="5" t="n">
         <v>38</v>
       </c>
@@ -8484,7 +8333,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I173" t="inlineStr"/>
       <c r="L173" s="5" t="n">
         <v>6</v>
       </c>
@@ -8528,7 +8376,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I174" t="inlineStr"/>
       <c r="L174" s="5" t="n">
         <v>38</v>
       </c>
@@ -8572,7 +8419,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I175" t="inlineStr"/>
       <c r="L175" s="5" t="n">
         <v>12</v>
       </c>
@@ -8616,7 +8462,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I176" t="inlineStr"/>
       <c r="L176" s="5" t="n">
         <v>9</v>
       </c>
@@ -8660,7 +8505,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I177" t="inlineStr"/>
       <c r="L177" s="5" t="n">
         <v>38</v>
       </c>
@@ -8704,7 +8548,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I178" t="inlineStr"/>
       <c r="L178" s="5" t="n">
         <v>22</v>
       </c>
@@ -8748,7 +8591,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I179" t="inlineStr"/>
       <c r="L179" s="5" t="n">
         <v>38</v>
       </c>
@@ -8792,7 +8634,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I180" t="inlineStr"/>
       <c r="L180" s="5" t="n">
         <v>55</v>
       </c>
@@ -8836,7 +8677,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I181" t="inlineStr"/>
       <c r="L181" s="5" t="n">
         <v>9</v>
       </c>
@@ -8880,7 +8720,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I182" t="inlineStr"/>
       <c r="L182" s="5" t="n">
         <v>9</v>
       </c>
@@ -8924,7 +8763,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I183" t="inlineStr"/>
       <c r="L183" s="5" t="n">
         <v>12</v>
       </c>
@@ -8968,7 +8806,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I184" t="inlineStr"/>
       <c r="L184" s="5" t="n">
         <v>38</v>
       </c>
@@ -9066,7 +8903,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I186" t="inlineStr"/>
       <c r="L186" s="5" t="n">
         <v>38</v>
       </c>
@@ -9110,7 +8946,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I187" t="inlineStr"/>
       <c r="L187" s="5" t="n">
         <v>31</v>
       </c>
@@ -9154,7 +8989,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I188" t="inlineStr"/>
       <c r="L188" s="5" t="n">
         <v>38</v>
       </c>
@@ -9198,7 +9032,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I189" t="inlineStr"/>
       <c r="L189" s="5" t="n">
         <v>31</v>
       </c>
@@ -9242,7 +9075,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I190" t="inlineStr"/>
       <c r="L190" s="5" t="n">
         <v>38</v>
       </c>
@@ -9340,7 +9172,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I192" t="inlineStr"/>
       <c r="L192" s="5" t="n">
         <v>6</v>
       </c>
@@ -9384,7 +9215,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I193" t="inlineStr"/>
       <c r="L193" s="5" t="n">
         <v>6</v>
       </c>
@@ -9428,7 +9258,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr"/>
       <c r="L194" s="5" t="n">
         <v>6</v>
       </c>
@@ -9472,7 +9301,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I195" t="inlineStr"/>
       <c r="L195" s="5" t="n">
         <v>9</v>
       </c>
@@ -9516,7 +9344,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I196" t="inlineStr"/>
       <c r="L196" s="5" t="n">
         <v>12</v>
       </c>
@@ -9614,7 +9441,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I198" t="inlineStr"/>
       <c r="L198" s="5" t="n">
         <v>22</v>
       </c>
@@ -9658,7 +9484,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I199" t="inlineStr"/>
       <c r="L199" s="5" t="n">
         <v>22</v>
       </c>
@@ -9702,7 +9527,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I200" t="inlineStr"/>
       <c r="L200" s="5" t="n">
         <v>38</v>
       </c>
@@ -9746,7 +9570,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I201" t="inlineStr"/>
       <c r="L201" s="5" t="n">
         <v>38</v>
       </c>
@@ -9790,7 +9613,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I202" t="inlineStr"/>
       <c r="L202" s="5" t="n">
         <v>6</v>
       </c>
@@ -9834,7 +9656,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I203" t="inlineStr"/>
       <c r="L203" s="5" t="n">
         <v>6</v>
       </c>
@@ -9878,7 +9699,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I204" t="inlineStr"/>
       <c r="L204" s="5" t="n">
         <v>6</v>
       </c>
@@ -9976,7 +9796,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I206" t="inlineStr"/>
       <c r="L206" s="5" t="n">
         <v>6</v>
       </c>
@@ -10020,7 +9839,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I207" t="inlineStr"/>
       <c r="L207" s="5" t="n">
         <v>9</v>
       </c>
@@ -10064,7 +9882,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I208" t="inlineStr"/>
       <c r="L208" s="5" t="n">
         <v>38</v>
       </c>
@@ -10162,7 +9979,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I210" t="inlineStr"/>
       <c r="L210" s="5" t="n">
         <v>12</v>
       </c>
@@ -10206,7 +10022,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I211" t="inlineStr"/>
       <c r="L211" s="5" t="n">
         <v>31</v>
       </c>
@@ -10250,7 +10065,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I212" t="inlineStr"/>
       <c r="L212" s="5" t="n">
         <v>38</v>
       </c>
@@ -10294,7 +10108,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I213" t="inlineStr"/>
       <c r="L213" s="5" t="n">
         <v>38</v>
       </c>
@@ -10338,7 +10151,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I214" t="inlineStr"/>
       <c r="L214" s="5" t="n">
         <v>12</v>
       </c>
@@ -10382,7 +10194,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I215" t="inlineStr"/>
       <c r="L215" s="5" t="n">
         <v>38</v>
       </c>
@@ -10426,7 +10237,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I216" t="inlineStr"/>
       <c r="L216" s="5" t="n">
         <v>55</v>
       </c>
@@ -10470,7 +10280,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I217" t="inlineStr"/>
       <c r="L217" s="5" t="n">
         <v>9</v>
       </c>
@@ -10514,7 +10323,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I218" t="inlineStr"/>
       <c r="L218" s="5" t="n">
         <v>22</v>
       </c>
@@ -10558,7 +10366,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I219" t="inlineStr"/>
       <c r="L219" s="5" t="n">
         <v>38</v>
       </c>
@@ -10602,7 +10409,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I220" t="inlineStr"/>
       <c r="L220" s="5" t="n">
         <v>12</v>
       </c>
@@ -10646,7 +10452,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I221" t="inlineStr"/>
       <c r="L221" s="5" t="n">
         <v>12</v>
       </c>
@@ -10690,7 +10495,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I222" t="inlineStr"/>
       <c r="L222" s="5" t="n">
         <v>22</v>
       </c>
@@ -10734,7 +10538,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I223" t="inlineStr"/>
       <c r="L223" s="5" t="n">
         <v>6</v>
       </c>
@@ -10778,7 +10581,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I224" t="inlineStr"/>
       <c r="L224" s="5" t="n">
         <v>6</v>
       </c>
@@ -10822,7 +10624,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I225" t="inlineStr"/>
       <c r="L225" s="5" t="n">
         <v>9</v>
       </c>
@@ -10866,7 +10667,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I226" t="inlineStr"/>
       <c r="L226" s="5" t="n">
         <v>22</v>
       </c>
@@ -10910,7 +10710,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I227" t="inlineStr"/>
       <c r="L227" s="5" t="n">
         <v>6</v>
       </c>
@@ -11008,7 +10807,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I229" t="inlineStr"/>
       <c r="L229" s="5" t="n">
         <v>6</v>
       </c>
@@ -11052,7 +10850,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I230" t="inlineStr"/>
       <c r="L230" s="5" t="n">
         <v>31</v>
       </c>
@@ -11096,7 +10893,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I231" t="inlineStr"/>
       <c r="L231" s="5" t="n">
         <v>22</v>
       </c>
@@ -11140,7 +10936,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I232" t="inlineStr"/>
       <c r="L232" s="5" t="n">
         <v>55</v>
       </c>
@@ -11184,7 +10979,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I233" t="inlineStr"/>
       <c r="L233" s="5" t="n">
         <v>6</v>
       </c>
@@ -11228,7 +11022,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I234" t="inlineStr"/>
       <c r="L234" s="5" t="n">
         <v>22</v>
       </c>
@@ -11374,7 +11167,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I237" t="inlineStr"/>
       <c r="L237" s="5" t="n">
         <v>6</v>
       </c>
@@ -11418,7 +11210,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I238" t="inlineStr"/>
       <c r="L238" s="5" t="n">
         <v>6</v>
       </c>
@@ -11462,7 +11253,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I239" t="inlineStr"/>
       <c r="L239" s="5" t="n">
         <v>38</v>
       </c>
@@ -11506,7 +11296,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I240" t="inlineStr"/>
       <c r="L240" s="5" t="n">
         <v>22</v>
       </c>
@@ -11550,7 +11339,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I241" t="inlineStr"/>
       <c r="L241" s="5" t="n">
         <v>22</v>
       </c>
@@ -11594,7 +11382,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I242" t="inlineStr"/>
       <c r="L242" s="5" t="n">
         <v>22</v>
       </c>
@@ -11638,7 +11425,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I243" t="inlineStr"/>
       <c r="L243" s="5" t="n">
         <v>12</v>
       </c>
@@ -11682,7 +11468,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I244" t="inlineStr"/>
       <c r="L244" s="5" t="n">
         <v>22</v>
       </c>
@@ -11726,7 +11511,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I245" t="inlineStr"/>
       <c r="L245" s="5" t="n">
         <v>9</v>
       </c>
@@ -11770,7 +11554,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I246" t="inlineStr"/>
       <c r="L246" s="5" t="n">
         <v>9</v>
       </c>
@@ -11814,7 +11597,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I247" t="inlineStr"/>
       <c r="L247" s="5" t="n">
         <v>55</v>
       </c>
@@ -11912,7 +11694,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I249" t="inlineStr"/>
       <c r="L249" s="5" t="n">
         <v>22</v>
       </c>
@@ -11956,7 +11737,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I250" t="inlineStr"/>
       <c r="L250" s="5" t="n">
         <v>22</v>
       </c>
@@ -12000,7 +11780,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I251" t="inlineStr"/>
       <c r="L251" s="5" t="n">
         <v>55</v>
       </c>
@@ -12044,7 +11823,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I252" t="inlineStr"/>
       <c r="L252" s="5" t="n">
         <v>38</v>
       </c>
@@ -12088,7 +11866,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I253" t="inlineStr"/>
       <c r="L253" s="5" t="n">
         <v>38</v>
       </c>
@@ -12132,7 +11909,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I254" t="inlineStr"/>
       <c r="L254" s="5" t="n">
         <v>22</v>
       </c>
@@ -12176,7 +11952,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I255" t="inlineStr"/>
       <c r="L255" s="5" t="n">
         <v>12</v>
       </c>
@@ -12220,7 +11995,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I256" t="inlineStr"/>
       <c r="L256" s="5" t="n">
         <v>38</v>
       </c>
@@ -12264,7 +12038,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I257" t="inlineStr"/>
       <c r="L257" s="5" t="n">
         <v>12</v>
       </c>
@@ -12308,7 +12081,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I258" t="inlineStr"/>
       <c r="L258" s="5" t="n">
         <v>22</v>
       </c>
@@ -12352,7 +12124,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I259" t="inlineStr"/>
       <c r="L259" s="5" t="n">
         <v>38</v>
       </c>
@@ -12396,7 +12167,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I260" t="inlineStr"/>
       <c r="L260" s="5" t="n">
         <v>9</v>
       </c>
@@ -12440,7 +12210,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I261" t="inlineStr"/>
       <c r="L261" s="5" t="n">
         <v>9</v>
       </c>
@@ -12484,7 +12253,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I262" t="inlineStr"/>
       <c r="L262" s="5" t="n">
         <v>6</v>
       </c>
@@ -12528,7 +12296,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I263" t="inlineStr"/>
       <c r="L263" s="5" t="n">
         <v>12</v>
       </c>
@@ -12572,7 +12339,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I264" t="inlineStr"/>
       <c r="L264" s="5" t="n">
         <v>38</v>
       </c>
@@ -12616,7 +12382,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I265" t="inlineStr"/>
       <c r="L265" s="5" t="n">
         <v>6</v>
       </c>
@@ -12660,7 +12425,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I266" t="inlineStr"/>
       <c r="L266" s="5" t="n">
         <v>38</v>
       </c>
@@ -12704,7 +12468,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I267" t="inlineStr"/>
       <c r="L267" s="5" t="n">
         <v>12</v>
       </c>
@@ -12748,7 +12511,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I268" t="inlineStr"/>
       <c r="L268" s="5" t="n">
         <v>38</v>
       </c>
@@ -12792,7 +12554,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I269" t="inlineStr"/>
       <c r="L269" s="5" t="n">
         <v>6</v>
       </c>
@@ -12836,7 +12597,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I270" t="inlineStr"/>
       <c r="L270" s="5" t="n">
         <v>9</v>
       </c>
@@ -12934,7 +12694,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I272" t="inlineStr"/>
       <c r="L272" s="5" t="n">
         <v>38</v>
       </c>
@@ -12978,7 +12737,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I273" t="inlineStr"/>
       <c r="L273" s="5" t="n">
         <v>38</v>
       </c>
@@ -13022,7 +12780,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I274" t="inlineStr"/>
       <c r="L274" s="5" t="n">
         <v>12</v>
       </c>
@@ -13066,7 +12823,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I275" t="inlineStr"/>
       <c r="L275" s="5" t="n">
         <v>38</v>
       </c>
@@ -13110,7 +12866,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I276" t="inlineStr"/>
       <c r="L276" s="5" t="n">
         <v>22</v>
       </c>
@@ -13154,7 +12909,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I277" t="inlineStr"/>
       <c r="L277" s="5" t="n">
         <v>22</v>
       </c>
@@ -13198,7 +12952,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I278" t="inlineStr"/>
       <c r="L278" s="5" t="n">
         <v>22</v>
       </c>
@@ -13242,7 +12995,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I279" t="inlineStr"/>
       <c r="L279" s="5" t="n">
         <v>31</v>
       </c>
@@ -13286,7 +13038,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I280" t="inlineStr"/>
       <c r="L280" s="5" t="n">
         <v>6</v>
       </c>
@@ -13330,7 +13081,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I281" t="inlineStr"/>
       <c r="L281" s="5" t="n">
         <v>6</v>
       </c>
@@ -13374,7 +13124,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I282" t="inlineStr"/>
       <c r="L282" s="5" t="n">
         <v>31</v>
       </c>
@@ -13418,7 +13167,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I283" t="inlineStr"/>
       <c r="L283" s="5" t="n">
         <v>9</v>
       </c>
@@ -13516,7 +13264,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I285" t="inlineStr"/>
       <c r="L285" s="5" t="n">
         <v>38</v>
       </c>
@@ -13560,7 +13307,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I286" t="inlineStr"/>
       <c r="L286" s="5" t="n">
         <v>9</v>
       </c>
@@ -13604,7 +13350,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I287" t="inlineStr"/>
       <c r="L287" s="5" t="n">
         <v>38</v>
       </c>
@@ -13648,7 +13393,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I288" t="inlineStr"/>
       <c r="L288" s="5" t="n">
         <v>12</v>
       </c>
@@ -13692,7 +13436,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I289" t="inlineStr"/>
       <c r="L289" s="5" t="n">
         <v>22</v>
       </c>
@@ -13736,7 +13479,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I290" t="inlineStr"/>
       <c r="L290" s="5" t="n">
         <v>6</v>
       </c>
@@ -13780,7 +13522,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I291" t="inlineStr"/>
       <c r="L291" s="5" t="n">
         <v>38</v>
       </c>
@@ -13878,7 +13619,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I293" t="inlineStr"/>
       <c r="L293" s="5" t="n">
         <v>38</v>
       </c>
@@ -13922,7 +13662,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I294" t="inlineStr"/>
       <c r="L294" s="5" t="n">
         <v>38</v>
       </c>
@@ -14020,7 +13759,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I296" t="inlineStr"/>
       <c r="L296" s="5" t="n">
         <v>12</v>
       </c>
@@ -14112,7 +13850,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I298" t="inlineStr"/>
       <c r="L298" s="5" t="n">
         <v>55</v>
       </c>
@@ -14156,7 +13893,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I299" t="inlineStr"/>
       <c r="L299" s="5" t="n">
         <v>12</v>
       </c>
@@ -14200,7 +13936,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I300" t="inlineStr"/>
       <c r="L300" s="5" t="n">
         <v>38</v>
       </c>
@@ -14244,7 +13979,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I301" t="inlineStr"/>
       <c r="L301" s="5" t="n">
         <v>38</v>
       </c>
@@ -14288,7 +14022,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I302" t="inlineStr"/>
       <c r="L302" s="5" t="n">
         <v>22</v>
       </c>
@@ -14332,7 +14065,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I303" t="inlineStr"/>
       <c r="L303" s="5" t="n">
         <v>55</v>
       </c>
@@ -14376,7 +14108,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I304" t="inlineStr"/>
       <c r="L304" s="5" t="n">
         <v>12</v>
       </c>
@@ -14420,7 +14151,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I305" t="inlineStr"/>
       <c r="L305" s="5" t="n">
         <v>55</v>
       </c>
@@ -14464,7 +14194,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I306" t="inlineStr"/>
       <c r="L306" s="5" t="n">
         <v>22</v>
       </c>
@@ -14508,7 +14237,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I307" t="inlineStr"/>
       <c r="L307" s="5" t="n">
         <v>6</v>
       </c>
@@ -14552,7 +14280,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I308" t="inlineStr"/>
       <c r="L308" s="5" t="n">
         <v>38</v>
       </c>
@@ -14596,7 +14323,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I309" t="inlineStr"/>
       <c r="L309" s="5" t="n">
         <v>6</v>
       </c>
@@ -14640,7 +14366,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I310" t="inlineStr"/>
       <c r="L310" s="5" t="n">
         <v>6</v>
       </c>
@@ -14684,7 +14409,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I311" t="inlineStr"/>
       <c r="L311" s="5" t="n">
         <v>9</v>
       </c>
@@ -14728,7 +14452,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I312" t="inlineStr"/>
       <c r="L312" s="5" t="n">
         <v>22</v>
       </c>
@@ -14772,7 +14495,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I313" t="inlineStr"/>
       <c r="L313" s="5" t="n">
         <v>38</v>
       </c>
@@ -14816,7 +14538,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I314" t="inlineStr"/>
       <c r="L314" s="5" t="n">
         <v>12</v>
       </c>
@@ -14860,7 +14581,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I315" t="inlineStr"/>
       <c r="L315" s="5" t="n">
         <v>12</v>
       </c>
@@ -14904,7 +14624,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I316" t="inlineStr"/>
       <c r="L316" s="5" t="n">
         <v>22</v>
       </c>
@@ -14948,7 +14667,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I317" t="inlineStr"/>
       <c r="L317" s="5" t="n">
         <v>38</v>
       </c>
@@ -14992,7 +14710,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I318" t="inlineStr"/>
       <c r="L318" s="5" t="n">
         <v>38</v>
       </c>
@@ -15036,7 +14753,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I319" t="inlineStr"/>
       <c r="L319" s="5" t="n">
         <v>12</v>
       </c>
@@ -15080,7 +14796,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I320" t="inlineStr"/>
       <c r="L320" s="5" t="n">
         <v>9</v>
       </c>
@@ -15124,7 +14839,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I321" t="inlineStr"/>
       <c r="L321" s="5" t="n">
         <v>55</v>
       </c>
@@ -15168,7 +14882,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I322" t="inlineStr"/>
       <c r="L322" s="5" t="n">
         <v>22</v>
       </c>
@@ -15212,7 +14925,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I323" t="inlineStr"/>
       <c r="L323" s="5" t="n">
         <v>38</v>
       </c>
@@ -15256,7 +14968,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I324" t="inlineStr"/>
       <c r="L324" s="5" t="n">
         <v>38</v>
       </c>
@@ -15300,7 +15011,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I325" t="inlineStr"/>
       <c r="L325" s="5" t="n">
         <v>38</v>
       </c>
@@ -15398,7 +15108,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I327" t="inlineStr"/>
       <c r="L327" s="5" t="n">
         <v>22</v>
       </c>
@@ -15442,7 +15151,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I328" t="inlineStr"/>
       <c r="L328" s="5" t="n">
         <v>6</v>
       </c>
@@ -15486,7 +15194,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I329" t="inlineStr"/>
       <c r="L329" s="5" t="n">
         <v>22</v>
       </c>
@@ -15530,7 +15237,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I330" t="inlineStr"/>
       <c r="L330" s="5" t="n">
         <v>9</v>
       </c>
@@ -15574,7 +15280,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I331" t="inlineStr"/>
       <c r="L331" s="5" t="n">
         <v>9</v>
       </c>
@@ -15618,7 +15323,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I332" t="inlineStr"/>
       <c r="L332" s="5" t="n">
         <v>31</v>
       </c>
@@ -15662,7 +15366,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I333" t="inlineStr"/>
       <c r="L333" s="5" t="n">
         <v>38</v>
       </c>
@@ -15706,7 +15409,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I334" t="inlineStr"/>
       <c r="L334" s="5" t="n">
         <v>38</v>
       </c>
@@ -15750,7 +15452,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I335" t="inlineStr"/>
       <c r="L335" s="5" t="n">
         <v>9</v>
       </c>
@@ -15794,7 +15495,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I336" t="inlineStr"/>
       <c r="L336" s="5" t="n">
         <v>38</v>
       </c>
@@ -15838,7 +15538,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I337" t="inlineStr"/>
       <c r="L337" s="5" t="n">
         <v>6</v>
       </c>
@@ -15882,7 +15581,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I338" t="inlineStr"/>
       <c r="L338" s="5" t="n">
         <v>38</v>
       </c>
@@ -15926,7 +15624,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I339" t="inlineStr"/>
       <c r="L339" s="5" t="n">
         <v>22</v>
       </c>
@@ -15970,7 +15667,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I340" t="inlineStr"/>
       <c r="L340" s="5" t="n">
         <v>6</v>
       </c>
@@ -16014,7 +15710,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I341" t="inlineStr"/>
       <c r="L341" s="5" t="n">
         <v>38</v>
       </c>
@@ -16058,7 +15753,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I342" t="inlineStr"/>
       <c r="L342" s="5" t="n">
         <v>38</v>
       </c>
@@ -16102,7 +15796,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I343" t="inlineStr"/>
       <c r="L343" s="5" t="n">
         <v>38</v>
       </c>
@@ -16146,7 +15839,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I344" t="inlineStr"/>
       <c r="L344" s="5" t="n">
         <v>22</v>
       </c>
@@ -16190,7 +15882,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I345" t="inlineStr"/>
       <c r="L345" s="5" t="n">
         <v>38</v>
       </c>
@@ -16234,7 +15925,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I346" t="inlineStr"/>
       <c r="L346" s="5" t="n">
         <v>38</v>
       </c>
@@ -16278,7 +15968,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I347" t="inlineStr"/>
       <c r="L347" s="5" t="n">
         <v>38</v>
       </c>
@@ -16322,7 +16011,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I348" t="inlineStr"/>
       <c r="L348" s="5" t="n">
         <v>12</v>
       </c>
@@ -16366,7 +16054,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I349" t="inlineStr"/>
       <c r="L349" s="5" t="n">
         <v>38</v>
       </c>
@@ -16464,7 +16151,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I351" t="inlineStr"/>
       <c r="L351" s="5" t="n">
         <v>6</v>
       </c>
@@ -16508,7 +16194,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I352" t="inlineStr"/>
       <c r="L352" s="5" t="n">
         <v>55</v>
       </c>
@@ -16552,7 +16237,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I353" t="inlineStr"/>
       <c r="L353" s="5" t="n">
         <v>9</v>
       </c>
@@ -16596,7 +16280,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I354" t="inlineStr"/>
       <c r="L354" s="5" t="n">
         <v>38</v>
       </c>
@@ -16640,7 +16323,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I355" t="inlineStr"/>
       <c r="L355" s="5" t="n">
         <v>6</v>
       </c>
@@ -16684,7 +16366,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I356" t="inlineStr"/>
       <c r="L356" s="5" t="n">
         <v>38</v>
       </c>
@@ -16728,7 +16409,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I357" t="inlineStr"/>
       <c r="L357" s="5" t="n">
         <v>12</v>
       </c>
@@ -16772,7 +16452,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I358" t="inlineStr"/>
       <c r="L358" s="5" t="n">
         <v>9</v>
       </c>
@@ -16816,7 +16495,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I359" t="inlineStr"/>
       <c r="L359" s="5" t="n">
         <v>55</v>
       </c>
@@ -16914,7 +16592,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I361" t="inlineStr"/>
       <c r="L361" s="5" t="n">
         <v>6</v>
       </c>
@@ -16958,7 +16635,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I362" t="inlineStr"/>
       <c r="L362" s="5" t="n">
         <v>22</v>
       </c>
@@ -17002,7 +16678,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I363" t="inlineStr"/>
       <c r="L363" s="5" t="n">
         <v>9</v>
       </c>
@@ -17046,7 +16721,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I364" t="inlineStr"/>
       <c r="L364" s="5" t="n">
         <v>22</v>
       </c>
@@ -17090,7 +16764,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I365" t="inlineStr"/>
       <c r="L365" s="5" t="n">
         <v>38</v>
       </c>
@@ -17182,7 +16855,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I367" t="inlineStr"/>
       <c r="L367" s="5" t="n">
         <v>31</v>
       </c>
@@ -17226,7 +16898,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I368" t="inlineStr"/>
       <c r="L368" s="5" t="n">
         <v>38</v>
       </c>
@@ -17270,7 +16941,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I369" t="inlineStr"/>
       <c r="L369" s="5" t="n">
         <v>9</v>
       </c>
@@ -17314,7 +16984,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I370" t="inlineStr"/>
       <c r="L370" s="5" t="n">
         <v>38</v>
       </c>
@@ -17358,7 +17027,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I371" t="inlineStr"/>
       <c r="L371" s="5" t="n">
         <v>6</v>
       </c>
@@ -17456,7 +17124,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I373" t="inlineStr"/>
       <c r="L373" s="5" t="n">
         <v>9</v>
       </c>
@@ -17500,7 +17167,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I374" t="inlineStr"/>
       <c r="L374" s="5" t="n">
         <v>22</v>
       </c>
@@ -17544,7 +17210,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I375" t="inlineStr"/>
       <c r="L375" s="5" t="n">
         <v>22</v>
       </c>
@@ -17588,7 +17253,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I376" t="inlineStr"/>
       <c r="L376" s="5" t="n">
         <v>22</v>
       </c>
@@ -17632,7 +17296,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I377" t="inlineStr"/>
       <c r="L377" s="5" t="n">
         <v>38</v>
       </c>
@@ -17676,7 +17339,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I378" t="inlineStr"/>
       <c r="L378" s="5" t="n">
         <v>38</v>
       </c>
@@ -17774,7 +17436,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I380" t="inlineStr"/>
       <c r="L380" s="5" t="n">
         <v>38</v>
       </c>
@@ -17818,7 +17479,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I381" t="inlineStr"/>
       <c r="L381" s="5" t="n">
         <v>38</v>
       </c>
@@ -17862,7 +17522,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I382" t="inlineStr"/>
       <c r="L382" s="5" t="n">
         <v>6</v>
       </c>
@@ -17906,7 +17565,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I383" t="inlineStr"/>
       <c r="L383" s="5" t="n">
         <v>22</v>
       </c>
@@ -18004,7 +17662,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I385" t="inlineStr"/>
       <c r="L385" s="5" t="n">
         <v>6</v>
       </c>
@@ -18048,7 +17705,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I386" t="inlineStr"/>
       <c r="L386" s="5" t="n">
         <v>12</v>
       </c>
@@ -18092,7 +17748,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I387" t="inlineStr"/>
       <c r="L387" s="5" t="n">
         <v>6</v>
       </c>
@@ -18136,7 +17791,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I388" t="inlineStr"/>
       <c r="L388" s="5" t="n">
         <v>12</v>
       </c>
@@ -18180,7 +17834,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I389" t="inlineStr"/>
       <c r="L389" s="5" t="n">
         <v>22</v>
       </c>
@@ -18224,7 +17877,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I390" t="inlineStr"/>
       <c r="L390" s="5" t="n">
         <v>38</v>
       </c>
@@ -18322,7 +17974,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I392" t="inlineStr"/>
       <c r="L392" s="5" t="n">
         <v>38</v>
       </c>
@@ -18366,7 +18017,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I393" t="inlineStr"/>
       <c r="L393" s="5" t="n">
         <v>38</v>
       </c>
@@ -18410,7 +18060,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I394" t="inlineStr"/>
       <c r="L394" s="5" t="n">
         <v>12</v>
       </c>
@@ -18454,7 +18103,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I395" t="inlineStr"/>
       <c r="L395" s="5" t="n">
         <v>22</v>
       </c>
@@ -18498,7 +18146,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I396" t="inlineStr"/>
       <c r="L396" s="5" t="n">
         <v>38</v>
       </c>
@@ -18596,7 +18243,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I398" t="inlineStr"/>
       <c r="L398" s="5" t="n">
         <v>12</v>
       </c>
@@ -18742,7 +18388,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I401" t="inlineStr"/>
       <c r="L401" s="5" t="n">
         <v>38</v>
       </c>
@@ -18786,7 +18431,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I402" t="inlineStr"/>
       <c r="L402" s="5" t="n">
         <v>38</v>
       </c>
@@ -18830,7 +18474,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I403" t="inlineStr"/>
       <c r="L403" s="5" t="n">
         <v>6</v>
       </c>
@@ -18874,7 +18517,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I404" t="inlineStr"/>
       <c r="L404" s="5" t="n">
         <v>22</v>
       </c>
@@ -18918,7 +18560,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I405" t="inlineStr"/>
       <c r="L405" s="5" t="n">
         <v>55</v>
       </c>
@@ -18962,7 +18603,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I406" t="inlineStr"/>
       <c r="L406" s="5" t="n">
         <v>6</v>
       </c>
@@ -19006,7 +18646,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I407" t="inlineStr"/>
       <c r="L407" s="5" t="n">
         <v>9</v>
       </c>
@@ -19050,7 +18689,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I408" t="inlineStr"/>
       <c r="L408" s="5" t="n">
         <v>38</v>
       </c>
@@ -19094,7 +18732,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I409" t="inlineStr"/>
       <c r="L409" s="5" t="n">
         <v>22</v>
       </c>
@@ -19138,7 +18775,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I410" t="inlineStr"/>
       <c r="L410" s="5" t="n">
         <v>38</v>
       </c>
@@ -19182,7 +18818,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I411" t="inlineStr"/>
       <c r="L411" s="5" t="n">
         <v>22</v>
       </c>
@@ -19226,7 +18861,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I412" t="inlineStr"/>
       <c r="L412" s="5" t="n">
         <v>38</v>
       </c>
@@ -19270,7 +18904,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I413" t="inlineStr"/>
       <c r="L413" s="5" t="n">
         <v>12</v>
       </c>
@@ -19314,7 +18947,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I414" t="inlineStr"/>
       <c r="L414" s="5" t="n">
         <v>55</v>
       </c>
@@ -19358,7 +18990,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I415" t="inlineStr"/>
       <c r="L415" s="5" t="n">
         <v>31</v>
       </c>
@@ -19402,7 +19033,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I416" t="inlineStr"/>
       <c r="L416" s="5" t="n">
         <v>31</v>
       </c>
@@ -19446,7 +19076,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I417" t="inlineStr"/>
       <c r="L417" s="5" t="n">
         <v>22</v>
       </c>
@@ -19490,7 +19119,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I418" t="inlineStr"/>
       <c r="L418" s="5" t="n">
         <v>38</v>
       </c>
@@ -19534,7 +19162,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I419" t="inlineStr"/>
       <c r="L419" s="5" t="n">
         <v>22</v>
       </c>
@@ -19578,7 +19205,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I420" t="inlineStr"/>
       <c r="L420" s="5" t="n">
         <v>38</v>
       </c>
@@ -19622,7 +19248,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I421" t="inlineStr"/>
       <c r="L421" s="5" t="n">
         <v>6</v>
       </c>
@@ -19666,7 +19291,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I422" t="inlineStr"/>
       <c r="L422" s="5" t="n">
         <v>22</v>
       </c>
@@ -19710,7 +19334,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I423" t="inlineStr"/>
       <c r="L423" s="5" t="n">
         <v>22</v>
       </c>
@@ -19754,7 +19377,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I424" t="inlineStr"/>
       <c r="L424" s="5" t="n">
         <v>22</v>
       </c>
@@ -19798,7 +19420,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I425" t="inlineStr"/>
       <c r="L425" s="5" t="n">
         <v>9</v>
       </c>
@@ -19890,7 +19511,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I427" t="inlineStr"/>
       <c r="L427" s="5" t="n">
         <v>55</v>
       </c>
@@ -19934,7 +19554,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I428" t="inlineStr"/>
       <c r="L428" s="5" t="n">
         <v>38</v>
       </c>
@@ -20026,7 +19645,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I430" t="inlineStr"/>
       <c r="L430" s="5" t="n">
         <v>38</v>
       </c>
@@ -20070,7 +19688,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I431" t="inlineStr"/>
       <c r="L431" s="5" t="n">
         <v>38</v>
       </c>
@@ -20114,7 +19731,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I432" t="inlineStr"/>
       <c r="L432" s="5" t="n">
         <v>38</v>
       </c>
@@ -20158,7 +19774,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I433" t="inlineStr"/>
       <c r="L433" s="5" t="n">
         <v>55</v>
       </c>
@@ -20202,7 +19817,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I434" t="inlineStr"/>
       <c r="L434" s="5" t="n">
         <v>6</v>
       </c>
@@ -20246,7 +19860,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I435" t="inlineStr"/>
       <c r="L435" s="5" t="n">
         <v>31</v>
       </c>
@@ -20290,7 +19903,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I436" t="inlineStr"/>
       <c r="L436" s="5" t="n">
         <v>9</v>
       </c>
@@ -20334,7 +19946,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I437" t="inlineStr"/>
       <c r="L437" s="5" t="n">
         <v>12</v>
       </c>
@@ -20378,7 +19989,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I438" t="inlineStr"/>
       <c r="L438" s="5" t="n">
         <v>31</v>
       </c>
@@ -20422,7 +20032,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I439" t="inlineStr"/>
       <c r="L439" s="5" t="n">
         <v>31</v>
       </c>
@@ -20466,7 +20075,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I440" t="inlineStr"/>
       <c r="L440" s="5" t="n">
         <v>31</v>
       </c>
@@ -20510,7 +20118,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I441" t="inlineStr"/>
       <c r="L441" s="5" t="n">
         <v>12</v>
       </c>
@@ -20554,7 +20161,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I442" t="inlineStr"/>
       <c r="L442" s="5" t="n">
         <v>12</v>
       </c>
@@ -20598,7 +20204,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I443" t="inlineStr"/>
       <c r="L443" s="5" t="n">
         <v>38</v>
       </c>
@@ -20642,7 +20247,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I444" t="inlineStr"/>
       <c r="L444" s="5" t="n">
         <v>22</v>
       </c>
@@ -20686,7 +20290,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I445" t="inlineStr"/>
       <c r="L445" s="5" t="n">
         <v>22</v>
       </c>
@@ -20730,7 +20333,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I446" t="inlineStr"/>
       <c r="L446" s="5" t="n">
         <v>38</v>
       </c>
@@ -20774,7 +20376,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I447" t="inlineStr"/>
       <c r="L447" s="5" t="n">
         <v>38</v>
       </c>
@@ -20872,7 +20473,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I449" t="inlineStr"/>
       <c r="L449" s="5" t="n">
         <v>6</v>
       </c>
@@ -20916,7 +20516,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I450" t="inlineStr"/>
       <c r="L450" s="5" t="n">
         <v>38</v>
       </c>
@@ -20960,7 +20559,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I451" t="inlineStr"/>
       <c r="L451" s="5" t="n">
         <v>55</v>
       </c>
@@ -21004,7 +20602,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I452" t="inlineStr"/>
       <c r="L452" s="5" t="n">
         <v>12</v>
       </c>
@@ -21048,7 +20645,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I453" t="inlineStr"/>
       <c r="L453" s="5" t="n">
         <v>38</v>
       </c>
@@ -21092,7 +20688,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I454" t="inlineStr"/>
       <c r="L454" s="5" t="n">
         <v>6</v>
       </c>
@@ -21136,7 +20731,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I455" t="inlineStr"/>
       <c r="L455" s="5" t="n">
         <v>6</v>
       </c>
@@ -21180,7 +20774,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I456" t="inlineStr"/>
       <c r="L456" s="5" t="n">
         <v>31</v>
       </c>
@@ -21224,7 +20817,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I457" t="inlineStr"/>
       <c r="L457" s="5" t="n">
         <v>6</v>
       </c>
@@ -21268,7 +20860,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I458" t="inlineStr"/>
       <c r="L458" s="5" t="n">
         <v>12</v>
       </c>
@@ -21312,7 +20903,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I459" t="inlineStr"/>
       <c r="L459" s="5" t="n">
         <v>31</v>
       </c>
@@ -21410,7 +21000,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I461" t="inlineStr"/>
       <c r="L461" s="5" t="n">
         <v>6</v>
       </c>
@@ -21454,7 +21043,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I462" t="inlineStr"/>
       <c r="L462" s="5" t="n">
         <v>22</v>
       </c>
@@ -21498,7 +21086,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I463" t="inlineStr"/>
       <c r="L463" s="5" t="n">
         <v>9</v>
       </c>
@@ -21542,7 +21129,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I464" t="inlineStr"/>
       <c r="L464" s="5" t="n">
         <v>6</v>
       </c>
@@ -21586,7 +21172,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I465" t="inlineStr"/>
       <c r="L465" s="5" t="n">
         <v>9</v>
       </c>
@@ -21630,7 +21215,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I466" t="inlineStr"/>
       <c r="L466" s="5" t="n">
         <v>9</v>
       </c>
@@ -21674,7 +21258,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I467" t="inlineStr"/>
       <c r="L467" s="5" t="n">
         <v>31</v>
       </c>
@@ -21718,7 +21301,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I468" t="inlineStr"/>
       <c r="L468" s="5" t="n">
         <v>22</v>
       </c>
@@ -21762,7 +21344,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I469" t="inlineStr"/>
       <c r="L469" s="5" t="n">
         <v>22</v>
       </c>
@@ -21806,7 +21387,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I470" t="inlineStr"/>
       <c r="L470" s="5" t="n">
         <v>9</v>
       </c>
@@ -21850,7 +21430,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I471" t="inlineStr"/>
       <c r="L471" s="5" t="n">
         <v>38</v>
       </c>
@@ -21894,7 +21473,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I472" t="inlineStr"/>
       <c r="L472" s="5" t="n">
         <v>6</v>
       </c>
@@ -21938,7 +21516,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I473" t="inlineStr"/>
       <c r="L473" s="5" t="n">
         <v>38</v>
       </c>
@@ -21982,7 +21559,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I474" t="inlineStr"/>
       <c r="L474" s="5" t="n">
         <v>38</v>
       </c>
@@ -22026,7 +21602,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I475" t="inlineStr"/>
       <c r="L475" s="5" t="n">
         <v>22</v>
       </c>
@@ -22070,7 +21645,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I476" t="inlineStr"/>
       <c r="L476" s="5" t="n">
         <v>55</v>
       </c>
@@ -22114,7 +21688,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I477" t="inlineStr"/>
       <c r="L477" s="5" t="n">
         <v>9</v>
       </c>
@@ -22158,7 +21731,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I478" t="inlineStr"/>
       <c r="L478" s="5" t="n">
         <v>6</v>
       </c>
@@ -22202,7 +21774,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I479" t="inlineStr"/>
       <c r="L479" s="5" t="n">
         <v>55</v>
       </c>
@@ -22246,7 +21817,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I480" t="inlineStr"/>
       <c r="L480" s="5" t="n">
         <v>38</v>
       </c>
@@ -22290,7 +21860,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I481" t="inlineStr"/>
       <c r="L481" s="5" t="n">
         <v>38</v>
       </c>
@@ -22334,7 +21903,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I482" t="inlineStr"/>
       <c r="L482" s="5" t="n">
         <v>38</v>
       </c>
@@ -22378,7 +21946,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I483" t="inlineStr"/>
       <c r="L483" s="5" t="n">
         <v>31</v>
       </c>
@@ -22422,7 +21989,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I484" t="inlineStr"/>
       <c r="L484" s="5" t="n">
         <v>31</v>
       </c>
@@ -22466,7 +22032,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I485" t="inlineStr"/>
       <c r="L485" s="5" t="n">
         <v>6</v>
       </c>
@@ -22510,7 +22075,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I486" t="inlineStr"/>
       <c r="L486" s="5" t="n">
         <v>38</v>
       </c>
@@ -22554,7 +22118,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I487" t="inlineStr"/>
       <c r="L487" s="5" t="n">
         <v>9</v>
       </c>
@@ -22598,7 +22161,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I488" t="inlineStr"/>
       <c r="L488" s="5" t="n">
         <v>31</v>
       </c>
@@ -22642,7 +22204,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I489" t="inlineStr"/>
       <c r="L489" s="5" t="n">
         <v>38</v>
       </c>
@@ -22686,7 +22247,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I490" t="inlineStr"/>
       <c r="L490" s="5" t="n">
         <v>38</v>
       </c>
@@ -22730,7 +22290,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I491" t="inlineStr"/>
       <c r="L491" s="5" t="n">
         <v>6</v>
       </c>
@@ -22822,7 +22381,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I493" t="inlineStr"/>
       <c r="L493" s="5" t="n">
         <v>38</v>
       </c>
@@ -22866,7 +22424,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I494" t="inlineStr"/>
       <c r="L494" s="5" t="n">
         <v>6</v>
       </c>
@@ -22964,7 +22521,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I496" t="inlineStr"/>
       <c r="L496" s="5" t="n">
         <v>22</v>
       </c>
@@ -23008,7 +22564,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I497" t="inlineStr"/>
       <c r="L497" s="5" t="n">
         <v>31</v>
       </c>
@@ -23052,7 +22607,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I498" t="inlineStr"/>
       <c r="L498" s="5" t="n">
         <v>31</v>
       </c>
@@ -23096,7 +22650,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I499" t="inlineStr"/>
       <c r="L499" s="5" t="n">
         <v>38</v>
       </c>
@@ -23140,7 +22693,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I500" t="inlineStr"/>
       <c r="L500" s="5" t="n">
         <v>38</v>
       </c>
@@ -23232,7 +22784,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I502" t="inlineStr"/>
       <c r="L502" s="5" t="n">
         <v>12</v>
       </c>
@@ -23276,7 +22827,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I503" t="inlineStr"/>
       <c r="L503" s="5" t="n">
         <v>38</v>
       </c>
@@ -23320,7 +22870,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I504" t="inlineStr"/>
       <c r="L504" s="5" t="n">
         <v>31</v>
       </c>
@@ -23364,7 +22913,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I505" t="inlineStr"/>
       <c r="L505" s="5" t="n">
         <v>6</v>
       </c>
@@ -23462,7 +23010,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I507" t="inlineStr"/>
       <c r="L507" s="5" t="n">
         <v>38</v>
       </c>
@@ -23506,7 +23053,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I508" t="inlineStr"/>
       <c r="L508" s="5" t="n">
         <v>9</v>
       </c>
@@ -23550,7 +23096,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I509" t="inlineStr"/>
       <c r="L509" s="5" t="n">
         <v>6</v>
       </c>
@@ -23594,7 +23139,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I510" t="inlineStr"/>
       <c r="L510" s="5" t="n">
         <v>38</v>
       </c>
@@ -23638,7 +23182,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I511" t="inlineStr"/>
       <c r="L511" s="5" t="n">
         <v>22</v>
       </c>
@@ -23736,7 +23279,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I513" t="inlineStr"/>
       <c r="L513" s="5" t="n">
         <v>22</v>
       </c>
@@ -23780,7 +23322,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I514" t="inlineStr"/>
       <c r="L514" s="5" t="n">
         <v>9</v>
       </c>
@@ -23824,7 +23365,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I515" t="inlineStr"/>
       <c r="L515" s="5" t="n">
         <v>55</v>
       </c>
@@ -23868,7 +23408,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I516" t="inlineStr"/>
       <c r="L516" s="5" t="n">
         <v>55</v>
       </c>
@@ -23912,7 +23451,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I517" t="inlineStr"/>
       <c r="L517" s="5" t="n">
         <v>6</v>
       </c>
@@ -23956,7 +23494,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I518" t="inlineStr"/>
       <c r="L518" s="5" t="n">
         <v>22</v>
       </c>
@@ -24000,7 +23537,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I519" t="inlineStr"/>
       <c r="L519" s="5" t="n">
         <v>6</v>
       </c>
@@ -24044,7 +23580,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I520" t="inlineStr"/>
       <c r="L520" s="5" t="n">
         <v>9</v>
       </c>
@@ -24088,7 +23623,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I521" t="inlineStr"/>
       <c r="L521" s="5" t="n">
         <v>22</v>
       </c>
@@ -24132,7 +23666,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I522" t="inlineStr"/>
       <c r="L522" s="5" t="n">
         <v>31</v>
       </c>
@@ -24176,7 +23709,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I523" t="inlineStr"/>
       <c r="L523" s="5" t="n">
         <v>38</v>
       </c>
@@ -24220,7 +23752,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I524" t="inlineStr"/>
       <c r="L524" s="5" t="n">
         <v>9</v>
       </c>
@@ -24318,7 +23849,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I526" t="inlineStr"/>
       <c r="L526" s="5" t="n">
         <v>12</v>
       </c>
@@ -24362,7 +23892,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I527" t="inlineStr"/>
       <c r="L527" s="5" t="n">
         <v>55</v>
       </c>
@@ -24406,7 +23935,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I528" t="inlineStr"/>
       <c r="L528" s="5" t="n">
         <v>31</v>
       </c>
@@ -24450,7 +23978,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I529" t="inlineStr"/>
       <c r="L529" s="5" t="n">
         <v>6</v>
       </c>
@@ -24494,7 +24021,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I530" t="inlineStr"/>
       <c r="L530" s="5" t="n">
         <v>12</v>
       </c>
@@ -24538,7 +24064,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I531" t="inlineStr"/>
       <c r="L531" s="5" t="n">
         <v>6</v>
       </c>
@@ -24582,7 +24107,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I532" t="inlineStr"/>
       <c r="L532" s="5" t="n">
         <v>9</v>
       </c>
@@ -24626,7 +24150,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I533" t="inlineStr"/>
       <c r="L533" s="5" t="n">
         <v>9</v>
       </c>
@@ -24670,7 +24193,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I534" t="inlineStr"/>
       <c r="L534" s="5" t="n">
         <v>6</v>
       </c>
@@ -24714,7 +24236,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I535" t="inlineStr"/>
       <c r="L535" s="5" t="n">
         <v>6</v>
       </c>
@@ -24758,7 +24279,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I536" t="inlineStr"/>
       <c r="L536" s="5" t="n">
         <v>12</v>
       </c>
@@ -24802,7 +24322,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I537" t="inlineStr"/>
       <c r="L537" s="5" t="n">
         <v>22</v>
       </c>
@@ -24846,7 +24365,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I538" t="inlineStr"/>
       <c r="L538" s="5" t="n">
         <v>55</v>
       </c>
@@ -24890,7 +24408,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I539" t="inlineStr"/>
       <c r="L539" s="5" t="n">
         <v>9</v>
       </c>
@@ -24934,7 +24451,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I540" t="inlineStr"/>
       <c r="L540" s="5" t="n">
         <v>22</v>
       </c>
@@ -24978,7 +24494,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I541" t="inlineStr"/>
       <c r="L541" s="5" t="n">
         <v>12</v>
       </c>
@@ -25022,7 +24537,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I542" t="inlineStr"/>
       <c r="L542" s="5" t="n">
         <v>6</v>
       </c>
@@ -25066,7 +24580,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I543" t="inlineStr"/>
       <c r="L543" s="5" t="n">
         <v>12</v>
       </c>
@@ -25110,7 +24623,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I544" t="inlineStr"/>
       <c r="L544" s="5" t="n">
         <v>12</v>
       </c>
@@ -25154,7 +24666,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I545" t="inlineStr"/>
       <c r="L545" s="5" t="n">
         <v>12</v>
       </c>
@@ -25198,7 +24709,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I546" t="inlineStr"/>
       <c r="L546" s="5" t="n">
         <v>9</v>
       </c>
@@ -25242,7 +24752,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I547" t="inlineStr"/>
       <c r="L547" s="5" t="n">
         <v>12</v>
       </c>
@@ -25286,7 +24795,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I548" t="inlineStr"/>
       <c r="L548" s="5" t="n">
         <v>55</v>
       </c>
@@ -25330,7 +24838,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I549" t="inlineStr"/>
       <c r="L549" s="5" t="n">
         <v>38</v>
       </c>
@@ -25422,7 +24929,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I551" t="inlineStr"/>
       <c r="L551" s="5" t="n">
         <v>22</v>
       </c>
@@ -25466,7 +24972,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I552" t="inlineStr"/>
       <c r="L552" s="5" t="n">
         <v>22</v>
       </c>
@@ -25510,7 +25015,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I553" t="inlineStr"/>
       <c r="L553" s="5" t="n">
         <v>31</v>
       </c>
@@ -25602,7 +25106,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I555" t="inlineStr"/>
       <c r="L555" s="5" t="n">
         <v>6</v>
       </c>
@@ -25646,7 +25149,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I556" t="inlineStr"/>
       <c r="L556" s="5" t="n">
         <v>6</v>
       </c>
@@ -25738,7 +25240,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I558" t="inlineStr"/>
       <c r="L558" s="5" t="n">
         <v>22</v>
       </c>
@@ -25782,7 +25283,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I559" t="inlineStr"/>
       <c r="L559" s="5" t="n">
         <v>31</v>
       </c>
@@ -25826,7 +25326,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I560" t="inlineStr"/>
       <c r="L560" s="5" t="n">
         <v>38</v>
       </c>
@@ -25870,7 +25369,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I561" t="inlineStr"/>
       <c r="L561" s="5" t="n">
         <v>9</v>
       </c>
@@ -25962,7 +25460,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I563" t="inlineStr"/>
       <c r="L563" s="5" t="n">
         <v>38</v>
       </c>
@@ -26006,7 +25503,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I564" t="inlineStr"/>
       <c r="L564" s="5" t="n">
         <v>38</v>
       </c>
@@ -26050,7 +25546,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I565" t="inlineStr"/>
       <c r="L565" s="5" t="n">
         <v>22</v>
       </c>
@@ -26094,7 +25589,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I566" t="inlineStr"/>
       <c r="L566" s="5" t="n">
         <v>22</v>
       </c>
@@ -26138,7 +25632,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I567" t="inlineStr"/>
       <c r="L567" s="5" t="n">
         <v>38</v>
       </c>
@@ -26182,7 +25675,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I568" t="inlineStr"/>
       <c r="L568" s="5" t="n">
         <v>12</v>
       </c>
@@ -26226,7 +25718,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I569" t="inlineStr"/>
       <c r="L569" s="5" t="n">
         <v>6</v>
       </c>
@@ -26270,7 +25761,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I570" t="inlineStr"/>
       <c r="L570" s="5" t="n">
         <v>38</v>
       </c>
@@ -26314,7 +25804,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I571" t="inlineStr"/>
       <c r="L571" s="5" t="n">
         <v>22</v>
       </c>
@@ -26358,7 +25847,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I572" t="inlineStr"/>
       <c r="L572" s="5" t="n">
         <v>31</v>
       </c>
@@ -26402,7 +25890,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I573" t="inlineStr"/>
       <c r="L573" s="5" t="n">
         <v>9</v>
       </c>
@@ -26494,7 +25981,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I575" t="inlineStr"/>
       <c r="L575" s="5" t="n">
         <v>22</v>
       </c>
@@ -26538,7 +26024,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I576" t="inlineStr"/>
       <c r="L576" s="5" t="n">
         <v>12</v>
       </c>
@@ -26582,7 +26067,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I577" t="inlineStr"/>
       <c r="L577" s="5" t="n">
         <v>9</v>
       </c>
@@ -26626,7 +26110,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I578" t="inlineStr"/>
       <c r="L578" s="5" t="n">
         <v>6</v>
       </c>
@@ -26670,7 +26153,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I579" t="inlineStr"/>
       <c r="L579" s="5" t="n">
         <v>38</v>
       </c>
@@ -26810,7 +26292,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I582" t="inlineStr"/>
       <c r="L582" s="5" t="n">
         <v>6</v>
       </c>
@@ -26854,7 +26335,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I583" t="inlineStr"/>
       <c r="L583" s="5" t="n">
         <v>6</v>
       </c>
@@ -26898,7 +26378,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I584" t="inlineStr"/>
       <c r="L584" s="5" t="n">
         <v>6</v>
       </c>
@@ -26942,7 +26421,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I585" t="inlineStr"/>
       <c r="L585" s="5" t="n">
         <v>9</v>
       </c>
@@ -26986,7 +26464,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I586" t="inlineStr"/>
       <c r="L586" s="5" t="n">
         <v>9</v>
       </c>
@@ -27030,7 +26507,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I587" t="inlineStr"/>
       <c r="L587" s="5" t="n">
         <v>12</v>
       </c>
@@ -27074,7 +26550,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I588" t="inlineStr"/>
       <c r="L588" s="5" t="n">
         <v>9</v>
       </c>
@@ -27118,7 +26593,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I589" t="inlineStr"/>
       <c r="L589" s="5" t="n">
         <v>38</v>
       </c>
@@ -27162,7 +26636,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I590" t="inlineStr"/>
       <c r="L590" s="5" t="n">
         <v>22</v>
       </c>
@@ -27206,7 +26679,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I591" t="inlineStr"/>
       <c r="L591" s="5" t="n">
         <v>9</v>
       </c>
@@ -27250,7 +26722,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I592" t="inlineStr"/>
       <c r="L592" s="5" t="n">
         <v>38</v>
       </c>
@@ -27294,7 +26765,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I593" t="inlineStr"/>
       <c r="L593" s="5" t="n">
         <v>22</v>
       </c>
@@ -27338,7 +26808,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I594" t="inlineStr"/>
       <c r="L594" s="5" t="n">
         <v>6</v>
       </c>
@@ -27382,7 +26851,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I595" t="inlineStr"/>
       <c r="L595" s="5" t="n">
         <v>6</v>
       </c>
@@ -27474,7 +26942,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I597" t="inlineStr"/>
       <c r="L597" s="5" t="n">
         <v>12</v>
       </c>
@@ -27518,7 +26985,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I598" t="inlineStr"/>
       <c r="L598" s="5" t="n">
         <v>31</v>
       </c>
@@ -27610,7 +27076,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I600" t="inlineStr"/>
       <c r="L600" s="5" t="n">
         <v>55</v>
       </c>
@@ -27783,12 +27248,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
@@ -27826,7 +27291,381 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>2 · A</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Create a sheet named Checks. Enter these labels and formulas exactly as written, then tell me each result:
+A1 Applications        B1 =ROWS(tblApps[Application_ID])
+A2 Hires               B2 =COUNTIFS(tblApps[Furthest_Stage],"Hired")
+A3 Offer acceptance    B3 =COUNTIFS(tblApps[Offer_Accepted],"Yes")/(COUNTIFS(tblApps[Offer_Accepted],"Yes")+COUNTIFS(tblApps[Offer_Accepted],"No"))
+A4 Avg time to hire    B4 =AVERAGEIFS(tblApps[Time_to_Hire_Days],tblApps[Furthest_Stage],"Hired")
+A5 Cost per hire       B5 =SUM(tblApps[Sourcing_Cost])/B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>3 · B</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>GOAL: Build a one-page H1 2026 recruitment KPI dashboard on the Dashboard sheet.
+CONTEXT: For BrightPath's Head of Recruitment; monthly review meeting.
+DATA: tblApps and tblTargets only. Use the KPI definitions on About_This_Data.
+CONSTRAINTS: Do not change tblApps or tblTargets. KPI cards must be formulas, not typed numbers.
+OUTPUT:
+  Row 1: title "Recruitment Dashboard - Jan to Jun 2026" and "Data as at 2026-06-30".
+  Row 3: five KPI cards - Applications, Hires, Offer acceptance rate, Avg time to hire (days), Cost per hire (S$).
+  Below: (1) column chart of hires by Hire_Date month with a line for Hire_Target from tblTargets,
+         (2) bar chart of hires by Sector sorted highest first,
+         (3) bar chart of applications by Source.
+  Slicers for Sector and Recruiter connected to all PivotTables. Put PivotTables on a sheet Dash_Data.
+REVIEW: List each KPI formula you will use before building.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>4 · C</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>The plan is approved. Build the dashboard exactly as planned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>5 · D</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Chat</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Compare each KPI card on the Dashboard with Checks!B1:B5, with no slicer selected. Show each card's formula, its value, the Checks value and whether they match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>5 · E</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Chat</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>The Offer acceptance rate card must exclude Offer_Accepted = "Pending". Change its formula to accepted / (accepted + declined) and show it as a percentage with 1 decimal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>6 · F</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Set the Sector slicer on the Dashboard to Technology only, then tell me the value on every KPI card.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>6 · G</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>On the Checks sheet, add these formulas in D1:D2 with labels in C1:C2, and tell me if they match the cards:
+=COUNTIFS(tblApps[Sector],"Technology")
+=COUNTIFS(tblApps[Sector],"Technology",tblApps[Furthest_Stage],"Hired")</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>6 · H</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Clear the Sector slicer so the dashboard shows all sectors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>6 · I</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Make the KPI cards respond to the Sector and Recruiter slicers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>7 · J</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Add a note under the title: "Source: tblApps; KPI definitions on About_This_Data".</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>7 · K</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Use one consistent colour scheme and align the charts in a grid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>7 · L</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Chat</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Review this dashboard for a Head of Recruitment. What is unclear or missing?</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>7 · M</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Prompt_Log already lists every prompt in this lab. For each one I ran, fill in What Copilot did and How I verified, and set Decision to Keep. I will tell you any row to change to Revise or Undo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Extra 1</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Plan a recruitment KPI dashboard on the Dashboard sheet from tblApps with KPI cards for applications, hires, offer acceptance rate, average time to hire and cost per hire. List the formulas before building.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Extra 2</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Create a KPI card that shows Cost per hire = total Sourcing_Cost / hires, formatted as S$ with 2 decimals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Extra 3</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Create a column chart of hires by Hire_Date month with Hire_Target from tblTargets as a line.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Extra 4</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Add slicers for Sector and Recruiter and connect them to all PivotTables on Dash_Data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Extra 5</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>The offer acceptance rate must exclude Pending offers. Update the formula and explain it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Extra 6</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Arrange the KPI cards in one row and the three charts in a grid below them with equal sizes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Extra 7</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Review this dashboard for a Head of Recruitment. What is unclear, missing or potentially misleading?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Extra 8</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Which recruiter made the most hires in H1 2026, and what was their average time to hire?</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
